--- a/corpus/C05.xlsx
+++ b/corpus/C05.xlsx
@@ -2871,8 +2871,8 @@
         <v>782125.0</v>
       </c>
       <c r="J7">
-        <f>J5+J6</f>
-        <v>817223.0</v>
+        <f>J5-J6</f>
+        <v>1203355.0</v>
       </c>
       <c r="K7">
         <f>K5+K6</f>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AA7">
         <f>SUM(C7:Z7)</f>
-        <v>25015346.0</v>
+        <v>25401478.0</v>
       </c>
     </row>
     <row r="8">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J8">
         <f>IF(J5=0,0,ROUND(J7/J5,4))</f>
-        <v>0.8089</v>
+        <v>1.1911</v>
       </c>
       <c r="K8">
         <f>IF(K5=0,0,ROUND(K7/K5,4))</f>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="J15">
         <f>J7+J13</f>
-        <v>457415.0</v>
+        <v>843547.0</v>
       </c>
       <c r="K15">
         <f>K7+K13</f>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AA15">
         <f>SUM(C15:Z15)</f>
-        <v>14183204.0</v>
+        <v>14569336.0</v>
       </c>
     </row>
     <row r="16">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="J16">
         <f>IF(J5=0,0,ROUND(J15/J5,4))</f>
-        <v>0.4528</v>
+        <v>0.835</v>
       </c>
       <c r="K16">
         <f>IF(K5=0,0,ROUND(K15/K5,4))</f>
@@ -3720,71 +3720,71 @@
       </c>
       <c r="J18">
         <f>I18+J15</f>
-        <v>3255968.0</v>
+        <v>3642100.0</v>
       </c>
       <c r="K18">
         <f>J18+K15</f>
-        <v>3731622.0</v>
+        <v>4117754.0</v>
       </c>
       <c r="L18">
         <f>K18+L15</f>
-        <v>4226869.0</v>
+        <v>4613001.0</v>
       </c>
       <c r="M18">
         <f>L18+M15</f>
-        <v>4743245.0</v>
+        <v>5129377.0</v>
       </c>
       <c r="N18">
         <f>M18+N15</f>
-        <v>5282258.0</v>
+        <v>5668390.0</v>
       </c>
       <c r="O18">
         <f>N18+O15</f>
-        <v>5845557.0</v>
+        <v>6231689.0</v>
       </c>
       <c r="P18">
         <f>O18+P15</f>
-        <v>6434812.0</v>
+        <v>6820944.0</v>
       </c>
       <c r="Q18">
         <f>P18+Q15</f>
-        <v>7051722.0</v>
+        <v>7437854.0</v>
       </c>
       <c r="R18">
         <f>Q18+R15</f>
-        <v>7698195.0</v>
+        <v>8084327.0</v>
       </c>
       <c r="S18">
         <f>R18+S15</f>
-        <v>8376096.0</v>
+        <v>8762228.0</v>
       </c>
       <c r="T18">
         <f>S18+T15</f>
-        <v>9087520.0</v>
+        <v>9473652.0</v>
       </c>
       <c r="U18">
         <f>T18+U15</f>
-        <v>9834567.0</v>
+        <v>10220699.0</v>
       </c>
       <c r="V18">
         <f>U18+V15</f>
-        <v>10619319.0</v>
+        <v>11005451.0</v>
       </c>
       <c r="W18">
         <f>V18+W15</f>
-        <v>11444101.0</v>
+        <v>11830233.0</v>
       </c>
       <c r="X18">
         <f>W18+X15</f>
-        <v>12311295.0</v>
+        <v>12697427.0</v>
       </c>
       <c r="Y18">
         <f>X18+Y15</f>
-        <v>13223487.0</v>
+        <v>13609619.0</v>
       </c>
       <c r="Z18">
         <f>Y18+Z15</f>
-        <v>14183204.0</v>
+        <v>14569336.0</v>
       </c>
     </row>
   </sheetData>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="B4">
         <f>'P&amp;L'!AA15</f>
-        <v>14183204.0</v>
+        <v>14569336.0</v>
       </c>
     </row>
     <row r="5">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="B11">
         <f>AVERAGE('P&amp;L'!C15:Z15)</f>
-        <v>590966.8333333334</v>
+        <v>607055.6666666666</v>
       </c>
     </row>
     <row r="12">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B14">
         <f>SUMIF('P&amp;L'!C15:Z15,"&gt;0")</f>
-        <v>14183204.0</v>
+        <v>14569336.0</v>
       </c>
     </row>
     <row r="15">
